--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127175097</v>
       </c>
       <c r="B2" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127242762</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>127174720</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>127243245</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,51 +1127,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127243662</v>
+        <v>127174601</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459490</v>
+        <v>459523</v>
       </c>
       <c r="R6" t="n">
-        <v>6696309</v>
+        <v>6696489</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,87 +1204,95 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera blommande stänglar</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174601</v>
+        <v>127243662</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459523</v>
+        <v>459490</v>
       </c>
       <c r="R7" t="n">
-        <v>6696489</v>
+        <v>6696309</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,90 +1319,67 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera blommande stänglar</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127243529</v>
+        <v>127244063</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>91284</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459477</v>
+        <v>459482</v>
       </c>
       <c r="R8" t="n">
-        <v>6696357</v>
+        <v>6696382</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1459,37 +1450,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127244063</v>
+        <v>127243529</v>
       </c>
       <c r="B9" t="n">
-        <v>91210</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459482</v>
+        <v>459477</v>
       </c>
       <c r="R9" t="n">
-        <v>6696382</v>
+        <v>6696357</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1563,7 +1563,7 @@
         <v>127243033</v>
       </c>
       <c r="B10" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>127244478</v>
       </c>
       <c r="B11" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>127242519</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127175097</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127242762</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>127174720</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127243245</v>
+        <v>127174601</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1055,22 +1055,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459450</v>
+        <v>459523</v>
       </c>
       <c r="R5" t="n">
-        <v>6696315</v>
+        <v>6696489</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,87 +1094,95 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flera blommande stänglar</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127174601</v>
+        <v>127243662</v>
       </c>
       <c r="B6" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459523</v>
+        <v>459490</v>
       </c>
       <c r="R6" t="n">
-        <v>6696489</v>
+        <v>6696309</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1204,81 +1209,76 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flera blommande stänglar</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127243662</v>
+        <v>127243245</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459490</v>
+        <v>459450</v>
       </c>
       <c r="R7" t="n">
-        <v>6696309</v>
+        <v>6696315</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1352,7 +1352,7 @@
         <v>127244063</v>
       </c>
       <c r="B8" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>127243529</v>
       </c>
       <c r="B9" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>127243033</v>
       </c>
       <c r="B10" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>127244478</v>
       </c>
       <c r="B11" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>127242519</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -1017,7 +1017,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174601</v>
+        <v>127243245</v>
       </c>
       <c r="B5" t="n">
         <v>98442</v>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1055,19 +1055,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459523</v>
+        <v>459450</v>
       </c>
       <c r="R5" t="n">
-        <v>6696489</v>
+        <v>6696315</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,95 +1097,87 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera blommande stänglar</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127243662</v>
+        <v>127174601</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459490</v>
+        <v>459523</v>
       </c>
       <c r="R6" t="n">
-        <v>6696309</v>
+        <v>6696489</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,76 +1204,81 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera blommande stänglar</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127243245</v>
+        <v>127243662</v>
       </c>
       <c r="B7" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459450</v>
+        <v>459490</v>
       </c>
       <c r="R7" t="n">
-        <v>6696315</v>
+        <v>6696309</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -1017,46 +1017,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127243245</v>
+        <v>127243662</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1064,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459450</v>
+        <v>459490</v>
       </c>
       <c r="R5" t="n">
-        <v>6696315</v>
+        <v>6696309</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1127,7 +1118,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127174601</v>
+        <v>127243245</v>
       </c>
       <c r="B6" t="n">
         <v>98442</v>
@@ -1157,7 +1148,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1165,19 +1156,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459523</v>
+        <v>459450</v>
       </c>
       <c r="R6" t="n">
-        <v>6696489</v>
+        <v>6696315</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1204,95 +1198,87 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flera blommande stänglar</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127243662</v>
+        <v>127174601</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459490</v>
+        <v>459523</v>
       </c>
       <c r="R7" t="n">
-        <v>6696309</v>
+        <v>6696489</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,30 +1305,44 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera blommande stänglar</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127175097</v>
       </c>
       <c r="B2" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127242762</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>127174720</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,51 +1017,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127243662</v>
+        <v>127174601</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459490</v>
+        <v>459523</v>
       </c>
       <c r="R5" t="n">
-        <v>6696309</v>
+        <v>6696489</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,30 +1094,44 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flera blommande stänglar</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1121,7 +1141,7 @@
         <v>127243245</v>
       </c>
       <c r="B6" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,57 +1248,51 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174601</v>
+        <v>127243662</v>
       </c>
       <c r="B7" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459523</v>
+        <v>459490</v>
       </c>
       <c r="R7" t="n">
-        <v>6696489</v>
+        <v>6696309</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,44 +1319,30 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera blommande stänglar</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1352,7 +1352,7 @@
         <v>127244063</v>
       </c>
       <c r="B8" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>127243529</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>127243033</v>
       </c>
       <c r="B10" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>127244478</v>
       </c>
       <c r="B11" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -1349,37 +1349,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127244063</v>
+        <v>127243529</v>
       </c>
       <c r="B8" t="n">
-        <v>91291</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1387,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459482</v>
+        <v>459477</v>
       </c>
       <c r="R8" t="n">
-        <v>6696382</v>
+        <v>6696357</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1450,46 +1459,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127243529</v>
+        <v>127244063</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>91291</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459477</v>
+        <v>459482</v>
       </c>
       <c r="R9" t="n">
-        <v>6696357</v>
+        <v>6696382</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -1017,7 +1017,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174601</v>
+        <v>127243245</v>
       </c>
       <c r="B5" t="n">
         <v>98443</v>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1055,19 +1055,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459523</v>
+        <v>459450</v>
       </c>
       <c r="R5" t="n">
-        <v>6696489</v>
+        <v>6696315</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,90 +1097,67 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera blommande stänglar</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127243245</v>
+        <v>127243662</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1185,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459450</v>
+        <v>459490</v>
       </c>
       <c r="R6" t="n">
-        <v>6696315</v>
+        <v>6696309</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1248,51 +1228,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127243662</v>
+        <v>127174601</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459490</v>
+        <v>459523</v>
       </c>
       <c r="R7" t="n">
-        <v>6696309</v>
+        <v>6696489</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,76 +1305,81 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera blommande stänglar</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127243529</v>
+        <v>127244063</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>91291</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459477</v>
+        <v>459482</v>
       </c>
       <c r="R8" t="n">
-        <v>6696357</v>
+        <v>6696382</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1459,37 +1450,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127244063</v>
+        <v>127243529</v>
       </c>
       <c r="B9" t="n">
-        <v>91291</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459482</v>
+        <v>459477</v>
       </c>
       <c r="R9" t="n">
-        <v>6696382</v>
+        <v>6696357</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -1127,51 +1127,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127243662</v>
+        <v>127174601</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459490</v>
+        <v>459523</v>
       </c>
       <c r="R6" t="n">
-        <v>6696309</v>
+        <v>6696489</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,87 +1204,95 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera blommande stänglar</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174601</v>
+        <v>127243662</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459523</v>
+        <v>459490</v>
       </c>
       <c r="R7" t="n">
-        <v>6696489</v>
+        <v>6696309</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,81 +1319,76 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera blommande stänglar</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127244063</v>
+        <v>127243529</v>
       </c>
       <c r="B8" t="n">
-        <v>91291</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1387,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459482</v>
+        <v>459477</v>
       </c>
       <c r="R8" t="n">
-        <v>6696382</v>
+        <v>6696357</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1450,46 +1459,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127243529</v>
+        <v>127244063</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>91291</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459477</v>
+        <v>459482</v>
       </c>
       <c r="R9" t="n">
-        <v>6696357</v>
+        <v>6696382</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -1127,57 +1127,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127174601</v>
+        <v>127243662</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459523</v>
+        <v>459490</v>
       </c>
       <c r="R6" t="n">
-        <v>6696489</v>
+        <v>6696309</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1204,95 +1198,87 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flera blommande stänglar</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127243662</v>
+        <v>127174601</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459490</v>
+        <v>459523</v>
       </c>
       <c r="R7" t="n">
-        <v>6696309</v>
+        <v>6696489</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,30 +1305,44 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera blommande stänglar</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127175097</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127242762</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>127174720</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>127243245</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>127243662</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>127174601</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,46 +1349,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127243529</v>
+        <v>127244063</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>91295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459477</v>
+        <v>459482</v>
       </c>
       <c r="R8" t="n">
-        <v>6696357</v>
+        <v>6696382</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1459,37 +1450,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127244063</v>
+        <v>127243529</v>
       </c>
       <c r="B9" t="n">
-        <v>91291</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459482</v>
+        <v>459477</v>
       </c>
       <c r="R9" t="n">
-        <v>6696382</v>
+        <v>6696357</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1563,7 +1563,7 @@
         <v>127243033</v>
       </c>
       <c r="B10" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>127244478</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>127242519</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -1127,51 +1127,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127243662</v>
+        <v>127174601</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459490</v>
+        <v>459523</v>
       </c>
       <c r="R6" t="n">
-        <v>6696309</v>
+        <v>6696489</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,87 +1204,95 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera blommande stänglar</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174601</v>
+        <v>127243662</v>
       </c>
       <c r="B7" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459523</v>
+        <v>459490</v>
       </c>
       <c r="R7" t="n">
-        <v>6696489</v>
+        <v>6696309</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,44 +1319,30 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera blommande stänglar</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127175097</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127242762</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>127174720</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127243245</v>
+        <v>127174601</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1055,22 +1055,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459450</v>
+        <v>459523</v>
       </c>
       <c r="R5" t="n">
-        <v>6696315</v>
+        <v>6696489</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,87 +1094,95 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flera blommande stänglar</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127174601</v>
+        <v>127243662</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459523</v>
+        <v>459490</v>
       </c>
       <c r="R6" t="n">
-        <v>6696489</v>
+        <v>6696309</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1204,81 +1209,76 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flera blommande stänglar</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127243662</v>
+        <v>127243245</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459490</v>
+        <v>459450</v>
       </c>
       <c r="R7" t="n">
-        <v>6696309</v>
+        <v>6696315</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1453,7 +1453,7 @@
         <v>127243529</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>127243033</v>
       </c>
       <c r="B10" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>127244478</v>
       </c>
       <c r="B11" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127175097</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127242762</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>127174720</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>127174601</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>127243662</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>127243245</v>
       </c>
       <c r="B7" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,37 +1349,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127244063</v>
+        <v>127243529</v>
       </c>
       <c r="B8" t="n">
-        <v>91295</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1387,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459482</v>
+        <v>459477</v>
       </c>
       <c r="R8" t="n">
-        <v>6696382</v>
+        <v>6696357</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1450,46 +1459,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127243529</v>
+        <v>127244063</v>
       </c>
       <c r="B9" t="n">
-        <v>98448</v>
+        <v>91297</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459477</v>
+        <v>459482</v>
       </c>
       <c r="R9" t="n">
-        <v>6696357</v>
+        <v>6696382</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1563,7 +1563,7 @@
         <v>127243033</v>
       </c>
       <c r="B10" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>127244478</v>
       </c>
       <c r="B11" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>127242519</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -1017,57 +1017,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174601</v>
+        <v>127243662</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459523</v>
+        <v>459490</v>
       </c>
       <c r="R5" t="n">
-        <v>6696489</v>
+        <v>6696309</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,95 +1088,87 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera blommande stänglar</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127243662</v>
+        <v>127174601</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459490</v>
+        <v>459523</v>
       </c>
       <c r="R6" t="n">
-        <v>6696309</v>
+        <v>6696489</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,30 +1195,44 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera blommande stänglar</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1349,46 +1349,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127243529</v>
+        <v>127244063</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>91297</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459477</v>
+        <v>459482</v>
       </c>
       <c r="R8" t="n">
-        <v>6696357</v>
+        <v>6696382</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1459,37 +1450,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127244063</v>
+        <v>127243529</v>
       </c>
       <c r="B9" t="n">
-        <v>91297</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459482</v>
+        <v>459477</v>
       </c>
       <c r="R9" t="n">
-        <v>6696382</v>
+        <v>6696357</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -1118,7 +1118,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127174601</v>
+        <v>127243245</v>
       </c>
       <c r="B6" t="n">
         <v>98450</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1156,19 +1156,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459523</v>
+        <v>459450</v>
       </c>
       <c r="R6" t="n">
-        <v>6696489</v>
+        <v>6696315</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,51 +1198,37 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flera blommande stänglar</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127243245</v>
+        <v>127174601</v>
       </c>
       <c r="B7" t="n">
         <v>98450</v>
@@ -1269,7 +1258,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1277,22 +1266,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459450</v>
+        <v>459523</v>
       </c>
       <c r="R7" t="n">
-        <v>6696315</v>
+        <v>6696489</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,30 +1305,44 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera blommande stänglar</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -1017,51 +1017,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127243662</v>
+        <v>127174601</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459490</v>
+        <v>459523</v>
       </c>
       <c r="R5" t="n">
-        <v>6696309</v>
+        <v>6696489</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,76 +1094,81 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flera blommande stänglar</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127243245</v>
+        <v>127243662</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1165,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459450</v>
+        <v>459490</v>
       </c>
       <c r="R6" t="n">
-        <v>6696315</v>
+        <v>6696309</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1228,7 +1239,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174601</v>
+        <v>127243245</v>
       </c>
       <c r="B7" t="n">
         <v>98450</v>
@@ -1258,7 +1269,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1266,19 +1277,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459523</v>
+        <v>459450</v>
       </c>
       <c r="R7" t="n">
-        <v>6696489</v>
+        <v>6696315</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,44 +1319,30 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera blommande stänglar</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127175097</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127242762</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>127174720</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,57 +1017,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174601</v>
+        <v>127243662</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459523</v>
+        <v>459490</v>
       </c>
       <c r="R5" t="n">
-        <v>6696489</v>
+        <v>6696309</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,81 +1088,76 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera blommande stänglar</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127243662</v>
+        <v>127243245</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>98456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1176,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459490</v>
+        <v>459450</v>
       </c>
       <c r="R6" t="n">
-        <v>6696309</v>
+        <v>6696315</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1239,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127243245</v>
+        <v>127174601</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1258,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1277,22 +1266,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459450</v>
+        <v>459523</v>
       </c>
       <c r="R7" t="n">
-        <v>6696315</v>
+        <v>6696489</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,30 +1305,44 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera blommande stänglar</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1352,7 +1352,7 @@
         <v>127244063</v>
       </c>
       <c r="B8" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>127243529</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>127243033</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>127244478</v>
       </c>
       <c r="B11" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127175097</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127242762</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>127174720</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>127243662</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>127243245</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>127174601</v>
       </c>
       <c r="B7" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>127244063</v>
       </c>
       <c r="B8" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>127243529</v>
       </c>
       <c r="B9" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>127243033</v>
       </c>
       <c r="B10" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>127244478</v>
       </c>
       <c r="B11" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>127242519</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127175097</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127242762</v>
       </c>
       <c r="B3" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>127174720</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,37 +1017,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127243662</v>
+        <v>127243245</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459490</v>
+        <v>459450</v>
       </c>
       <c r="R5" t="n">
-        <v>6696309</v>
+        <v>6696315</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1118,46 +1127,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127243245</v>
+        <v>127243662</v>
       </c>
       <c r="B6" t="n">
-        <v>98459</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459450</v>
+        <v>459490</v>
       </c>
       <c r="R6" t="n">
-        <v>6696315</v>
+        <v>6696309</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1231,7 +1231,7 @@
         <v>127174601</v>
       </c>
       <c r="B7" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,37 +1349,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127244063</v>
+        <v>127243529</v>
       </c>
       <c r="B8" t="n">
-        <v>91306</v>
+        <v>98467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1387,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459482</v>
+        <v>459477</v>
       </c>
       <c r="R8" t="n">
-        <v>6696382</v>
+        <v>6696357</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1450,46 +1459,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127243529</v>
+        <v>127244063</v>
       </c>
       <c r="B9" t="n">
-        <v>98459</v>
+        <v>91314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459477</v>
+        <v>459482</v>
       </c>
       <c r="R9" t="n">
-        <v>6696357</v>
+        <v>6696382</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1563,7 +1563,7 @@
         <v>127243033</v>
       </c>
       <c r="B10" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>127244478</v>
       </c>
       <c r="B11" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>127242519</v>
       </c>
       <c r="B12" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127175097</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127242762</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>127174720</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,46 +1017,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127243245</v>
+        <v>127243662</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1064,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459450</v>
+        <v>459490</v>
       </c>
       <c r="R5" t="n">
-        <v>6696315</v>
+        <v>6696309</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1127,37 +1118,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127243662</v>
+        <v>127243245</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459490</v>
+        <v>459450</v>
       </c>
       <c r="R6" t="n">
-        <v>6696309</v>
+        <v>6696315</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1231,7 +1231,7 @@
         <v>127174601</v>
       </c>
       <c r="B7" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,46 +1349,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127243529</v>
+        <v>127244063</v>
       </c>
       <c r="B8" t="n">
-        <v>98467</v>
+        <v>91315</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459477</v>
+        <v>459482</v>
       </c>
       <c r="R8" t="n">
-        <v>6696357</v>
+        <v>6696382</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1459,37 +1450,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127244063</v>
+        <v>127243529</v>
       </c>
       <c r="B9" t="n">
-        <v>91314</v>
+        <v>98468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459482</v>
+        <v>459477</v>
       </c>
       <c r="R9" t="n">
-        <v>6696382</v>
+        <v>6696357</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1563,7 +1563,7 @@
         <v>127243033</v>
       </c>
       <c r="B10" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>127244478</v>
       </c>
       <c r="B11" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127175097</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127242762</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>127174720</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,37 +1017,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127243662</v>
+        <v>127243245</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459490</v>
+        <v>459450</v>
       </c>
       <c r="R5" t="n">
-        <v>6696309</v>
+        <v>6696315</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1118,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127243245</v>
+        <v>127174601</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,7 +1157,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1156,22 +1165,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459450</v>
+        <v>459523</v>
       </c>
       <c r="R6" t="n">
-        <v>6696315</v>
+        <v>6696489</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,87 +1204,95 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera blommande stänglar</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174601</v>
+        <v>127243662</v>
       </c>
       <c r="B7" t="n">
-        <v>98468</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459523</v>
+        <v>459490</v>
       </c>
       <c r="R7" t="n">
-        <v>6696489</v>
+        <v>6696309</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,44 +1319,30 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera blommande stänglar</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1352,7 +1352,7 @@
         <v>127244063</v>
       </c>
       <c r="B8" t="n">
-        <v>91315</v>
+        <v>91284</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>127243529</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>127243033</v>
       </c>
       <c r="B10" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>127244478</v>
       </c>
       <c r="B11" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>127242519</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127175097</v>
+        <v>127244063</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459453</v>
+        <v>459482</v>
       </c>
       <c r="R2" t="n">
-        <v>6696400</v>
+        <v>6696382</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,49 +746,40 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127242762</v>
+        <v>127242519</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,35 +787,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459419</v>
+        <v>459397</v>
       </c>
       <c r="R3" t="n">
-        <v>6696311</v>
+        <v>6696289</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -901,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127174720</v>
+        <v>127243662</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,46 +888,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459424</v>
+        <v>459490</v>
       </c>
       <c r="R4" t="n">
-        <v>6696607</v>
+        <v>6696309</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,49 +948,40 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127243662</v>
+        <v>127174966</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,40 +989,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459490</v>
+        <v>459432</v>
       </c>
       <c r="R5" t="n">
-        <v>6696309</v>
+        <v>6696511</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,40 +1046,54 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gammal stor sälg.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127243245</v>
+        <v>127174601</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,7 +1120,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1156,22 +1128,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459450</v>
+        <v>459523</v>
       </c>
       <c r="R6" t="n">
-        <v>6696315</v>
+        <v>6696489</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,40 +1167,54 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera blommande stänglar</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174601</v>
+        <v>127174720</v>
       </c>
       <c r="B7" t="n">
-        <v>98468</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,7 +1241,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1272,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459523</v>
+        <v>459424</v>
       </c>
       <c r="R7" t="n">
-        <v>6696489</v>
+        <v>6696607</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1307,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1317,12 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera blommande stänglar</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,51 +1327,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127244063</v>
+        <v>127175097</v>
       </c>
       <c r="B8" t="n">
-        <v>91315</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459482</v>
+        <v>459453</v>
       </c>
       <c r="R8" t="n">
-        <v>6696382</v>
+        <v>6696400</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,40 +1404,49 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127243529</v>
+        <v>127242762</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,7 +1473,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1497,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459477</v>
+        <v>459419</v>
       </c>
       <c r="R9" t="n">
-        <v>6696357</v>
+        <v>6696311</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1563,7 +1556,7 @@
         <v>127243033</v>
       </c>
       <c r="B10" t="n">
-        <v>98468</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127244478</v>
+        <v>127243245</v>
       </c>
       <c r="B11" t="n">
-        <v>98468</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,10 +1693,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1713,10 +1710,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459418</v>
+        <v>459450</v>
       </c>
       <c r="R11" t="n">
-        <v>6696365</v>
+        <v>6696315</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1776,37 +1773,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127242519</v>
+        <v>127243529</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1814,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459397</v>
+        <v>459477</v>
       </c>
       <c r="R12" t="n">
-        <v>6696289</v>
+        <v>6696357</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1874,6 +1880,112 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127244478</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>459418</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6696365</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -978,48 +978,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174966</v>
+        <v>135269155</v>
       </c>
       <c r="B5" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459432</v>
+        <v>459667</v>
       </c>
       <c r="R5" t="n">
-        <v>6696511</v>
+        <v>6696747</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1043,27 +1046,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal stor sälg.</t>
+          <t>i Tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,28 +1075,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127174601</v>
+        <v>135269308</v>
       </c>
       <c r="B6" t="n">
-        <v>99118</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1101,46 +1105,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459523</v>
+        <v>459706</v>
       </c>
       <c r="R6" t="n">
-        <v>6696489</v>
+        <v>6696723</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1164,27 +1162,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera blommande stänglar</t>
+          <t>Högt upp i Tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,75 +1191,67 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174720</v>
+        <v>127174966</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459424</v>
+        <v>459432</v>
       </c>
       <c r="R7" t="n">
-        <v>6696607</v>
+        <v>6696511</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1290,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gammal stor sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,57 +1322,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127175097</v>
+        <v>135269344</v>
       </c>
       <c r="B8" t="n">
-        <v>99118</v>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459453</v>
+        <v>459672</v>
       </c>
       <c r="R8" t="n">
-        <v>6696400</v>
+        <v>6696703</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1401,22 +1395,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,58 +1430,54 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127242762</v>
+        <v>135269440</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1490,13 +1485,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459419</v>
+        <v>459559</v>
       </c>
       <c r="R9" t="n">
-        <v>6696311</v>
+        <v>6696684</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1520,12 +1515,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,26 +1544,25 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127243033</v>
+        <v>127174601</v>
       </c>
       <c r="B10" t="n">
         <v>99118</v>
@@ -1583,7 +1592,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1591,22 +1600,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459437</v>
+        <v>459523</v>
       </c>
       <c r="R10" t="n">
-        <v>6696342</v>
+        <v>6696489</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1633,37 +1639,51 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Flera blommande stänglar</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127243245</v>
+        <v>127174720</v>
       </c>
       <c r="B11" t="n">
         <v>99118</v>
@@ -1693,7 +1713,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1701,22 +1721,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459450</v>
+        <v>459424</v>
       </c>
       <c r="R11" t="n">
-        <v>6696315</v>
+        <v>6696607</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1743,37 +1760,46 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127243529</v>
+        <v>127175097</v>
       </c>
       <c r="B12" t="n">
         <v>99118</v>
@@ -1803,7 +1829,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1811,22 +1837,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459477</v>
+        <v>459453</v>
       </c>
       <c r="R12" t="n">
-        <v>6696357</v>
+        <v>6696400</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1853,37 +1876,46 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127244478</v>
+        <v>127242762</v>
       </c>
       <c r="B13" t="n">
         <v>99118</v>
@@ -1913,10 +1945,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1926,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459418</v>
+        <v>459419</v>
       </c>
       <c r="R13" t="n">
-        <v>6696365</v>
+        <v>6696311</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1986,6 +2022,802 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127243033</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>459437</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6696342</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127243245</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>459450</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6696315</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127243529</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>459477</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6696357</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127244478</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>459418</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6696365</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135267983</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Butjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>459580</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6696691</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135269228</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>459755</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6696734</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2st m stjälk</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135269382</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>459654</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6696700</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>silvertejpmarkerad men ej inlagt i artportalen tidigare</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1322,27 +1322,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135269344</v>
+        <v>135475891</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1361,17 +1361,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459672</v>
+        <v>459499</v>
       </c>
       <c r="R8" t="n">
-        <v>6696703</v>
+        <v>6696373</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1395,27 +1395,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>födosökshack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,19 +1420,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135269440</v>
+        <v>135269344</v>
       </c>
       <c r="B9" t="n">
         <v>57975</v>
@@ -1485,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459559</v>
+        <v>459672</v>
       </c>
       <c r="R9" t="n">
-        <v>6696684</v>
+        <v>6696703</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1535,7 +1525,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,57 +1552,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127174601</v>
+        <v>135269440</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>57975</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459523</v>
+        <v>459559</v>
       </c>
       <c r="R10" t="n">
-        <v>6696489</v>
+        <v>6696684</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1636,27 +1625,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flera blommande stänglar</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,19 +1660,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127174720</v>
+        <v>127174601</v>
       </c>
       <c r="B11" t="n">
         <v>99118</v>
@@ -1713,7 +1702,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1727,10 +1716,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459424</v>
+        <v>459523</v>
       </c>
       <c r="R11" t="n">
-        <v>6696607</v>
+        <v>6696489</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1762,7 +1751,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1761,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Flera blommande stänglar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,7 +1793,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127175097</v>
+        <v>127174720</v>
       </c>
       <c r="B12" t="n">
         <v>99118</v>
@@ -1829,7 +1823,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1843,13 +1837,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459453</v>
+        <v>459424</v>
       </c>
       <c r="R12" t="n">
-        <v>6696400</v>
+        <v>6696607</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,7 +1872,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1888,7 +1882,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,7 +1909,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127242762</v>
+        <v>127175097</v>
       </c>
       <c r="B13" t="n">
         <v>99118</v>
@@ -1945,7 +1939,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1953,22 +1947,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459419</v>
+        <v>459453</v>
       </c>
       <c r="R13" t="n">
-        <v>6696311</v>
+        <v>6696400</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,37 +1986,46 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127243033</v>
+        <v>127242762</v>
       </c>
       <c r="B14" t="n">
         <v>99118</v>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459437</v>
+        <v>459419</v>
       </c>
       <c r="R14" t="n">
-        <v>6696342</v>
+        <v>6696311</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2135,7 +2135,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127243245</v>
+        <v>127243033</v>
       </c>
       <c r="B15" t="n">
         <v>99118</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459450</v>
+        <v>459437</v>
       </c>
       <c r="R15" t="n">
-        <v>6696315</v>
+        <v>6696342</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2245,7 +2245,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127243529</v>
+        <v>127243245</v>
       </c>
       <c r="B16" t="n">
         <v>99118</v>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459477</v>
+        <v>459450</v>
       </c>
       <c r="R16" t="n">
-        <v>6696357</v>
+        <v>6696315</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2355,7 +2355,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127244478</v>
+        <v>127243529</v>
       </c>
       <c r="B17" t="n">
         <v>99118</v>
@@ -2388,7 +2388,11 @@
           <t>20</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2398,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459418</v>
+        <v>459477</v>
       </c>
       <c r="R17" t="n">
-        <v>6696365</v>
+        <v>6696357</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2461,10 +2465,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135267983</v>
+        <v>127244478</v>
       </c>
       <c r="B18" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2491,27 +2495,23 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Butjärnsberget, Dlr</t>
+          <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459580</v>
+        <v>459418</v>
       </c>
       <c r="R18" t="n">
-        <v>6696691</v>
+        <v>6696365</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2538,12 +2538,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,7 +2571,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135269228</v>
+        <v>135267983</v>
       </c>
       <c r="B19" t="n">
         <v>99195</v>
@@ -2614,17 +2614,17 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459755</v>
+        <v>459580</v>
       </c>
       <c r="R19" t="n">
-        <v>6696734</v>
+        <v>6696691</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2651,24 +2651,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2st m stjälk</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2684,19 +2669,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135269382</v>
+        <v>135269228</v>
       </c>
       <c r="B20" t="n">
         <v>99195</v>
@@ -2726,7 +2711,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2743,10 +2728,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459654</v>
+        <v>459755</v>
       </c>
       <c r="R20" t="n">
-        <v>6696700</v>
+        <v>6696734</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2793,7 +2778,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>silvertejpmarkerad men ej inlagt i artportalen tidigare</t>
+          <t>2st m stjälk</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,6 +2803,241 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135269382</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>459654</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6696700</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>silvertejpmarkerad men ej inlagt i artportalen tidigare</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135475860</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Butjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>459335</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6696521</v>
+      </c>
+      <c r="S22" t="n">
+        <v>50</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127244063</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127242519</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127243662</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269155</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269308</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127174966</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1429,6 +1464,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135475891</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1549,6 +1589,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269344</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1669,6 +1714,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269440</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1790,6 +1840,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127174601</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1906,6 +1961,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127174720</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2022,6 +2082,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127175097</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2132,6 +2197,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127242762</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2242,6 +2312,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127243033</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2352,6 +2427,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127243245</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2462,6 +2542,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127243529</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2568,6 +2653,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127244478</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2678,6 +2768,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135267983</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2803,6 +2898,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269228</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2928,6 +3028,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269382</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3038,8 +3143,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135475860</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ22"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,7 +1001,7 @@
         <v>135269155</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>135269308</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,48 +1240,51 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174966</v>
+        <v>135661458</v>
       </c>
       <c r="B7" t="n">
-        <v>80432</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459432</v>
+        <v>459376</v>
       </c>
       <c r="R7" t="n">
-        <v>6696511</v>
+        <v>6696540</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,27 +1308,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal stor sälg.</t>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,79 +1327,72 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127174966</t>
+          <t>https://artportalen.se/Sighting/135661458</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135475891</v>
+        <v>127174966</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Butjärnsberget, Dlr</t>
+          <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459499</v>
+        <v>459432</v>
       </c>
       <c r="R8" t="n">
-        <v>6696373</v>
+        <v>6696511</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,17 +1416,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>födosökshack på tall</t>
+          <t>På gammal stor sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,44 +1451,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135475891</t>
+          <t>https://artportalen.se/Sighting/127174966</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135269344</v>
+        <v>135475891</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>57977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1511,17 +1507,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459672</v>
+        <v>459499</v>
       </c>
       <c r="R9" t="n">
-        <v>6696703</v>
+        <v>6696373</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1545,27 +1541,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>födosökshack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,27 +1566,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135269344</t>
+          <t>https://artportalen.se/Sighting/135475891</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135269440</v>
+        <v>135269344</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459559</v>
+        <v>459672</v>
       </c>
       <c r="R10" t="n">
-        <v>6696684</v>
+        <v>6696703</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,7 +1676,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,63 +1702,62 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135269440</t>
+          <t>https://artportalen.se/Sighting/135269344</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127174601</v>
+        <v>135269440</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459523</v>
+        <v>459559</v>
       </c>
       <c r="R11" t="n">
-        <v>6696489</v>
+        <v>6696684</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1796,27 +1781,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Flera blommande stänglar</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1831,24 +1816,24 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127174601</t>
+          <t>https://artportalen.se/Sighting/135269440</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127174720</v>
+        <v>127174601</v>
       </c>
       <c r="B12" t="n">
         <v>99118</v>
@@ -1878,7 +1863,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1892,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459424</v>
+        <v>459523</v>
       </c>
       <c r="R12" t="n">
-        <v>6696607</v>
+        <v>6696489</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1927,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1937,7 +1922,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Flera blommande stänglar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1963,13 +1953,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127174720</t>
+          <t>https://artportalen.se/Sighting/127174601</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127175097</v>
+        <v>127174720</v>
       </c>
       <c r="B13" t="n">
         <v>99118</v>
@@ -1999,7 +1989,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2013,13 +2003,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459453</v>
+        <v>459424</v>
       </c>
       <c r="R13" t="n">
-        <v>6696400</v>
+        <v>6696607</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2048,7 +2038,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2058,7 +2048,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2084,13 +2074,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127175097</t>
+          <t>https://artportalen.se/Sighting/127174720</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127242762</v>
+        <v>127175097</v>
       </c>
       <c r="B14" t="n">
         <v>99118</v>
@@ -2120,7 +2110,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2128,22 +2118,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459419</v>
+        <v>459453</v>
       </c>
       <c r="R14" t="n">
-        <v>6696311</v>
+        <v>6696400</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2170,42 +2157,51 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127242762</t>
+          <t>https://artportalen.se/Sighting/127175097</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127243033</v>
+        <v>127242762</v>
       </c>
       <c r="B15" t="n">
         <v>99118</v>
@@ -2252,10 +2248,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459437</v>
+        <v>459419</v>
       </c>
       <c r="R15" t="n">
-        <v>6696342</v>
+        <v>6696311</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2314,13 +2310,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127243033</t>
+          <t>https://artportalen.se/Sighting/127242762</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127243245</v>
+        <v>127243033</v>
       </c>
       <c r="B16" t="n">
         <v>99118</v>
@@ -2350,7 +2346,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2367,10 +2363,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459450</v>
+        <v>459437</v>
       </c>
       <c r="R16" t="n">
-        <v>6696315</v>
+        <v>6696342</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2429,13 +2425,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127243245</t>
+          <t>https://artportalen.se/Sighting/127243033</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127243529</v>
+        <v>127243245</v>
       </c>
       <c r="B17" t="n">
         <v>99118</v>
@@ -2465,7 +2461,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2482,10 +2478,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459477</v>
+        <v>459450</v>
       </c>
       <c r="R17" t="n">
-        <v>6696357</v>
+        <v>6696315</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2544,13 +2540,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127243529</t>
+          <t>https://artportalen.se/Sighting/127243245</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127244478</v>
+        <v>127243529</v>
       </c>
       <c r="B18" t="n">
         <v>99118</v>
@@ -2583,7 +2579,11 @@
           <t>20</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459418</v>
+        <v>459477</v>
       </c>
       <c r="R18" t="n">
-        <v>6696365</v>
+        <v>6696357</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2655,16 +2655,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127244478</t>
+          <t>https://artportalen.se/Sighting/127243529</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135267983</v>
+        <v>127244478</v>
       </c>
       <c r="B19" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2691,27 +2691,23 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Butjärnsberget, Dlr</t>
+          <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459580</v>
+        <v>459418</v>
       </c>
       <c r="R19" t="n">
-        <v>6696691</v>
+        <v>6696365</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2738,12 +2734,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2770,16 +2766,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135267983</t>
+          <t>https://artportalen.se/Sighting/127244478</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135269228</v>
+        <v>135267983</v>
       </c>
       <c r="B20" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,17 +2815,17 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459755</v>
+        <v>459580</v>
       </c>
       <c r="R20" t="n">
-        <v>6696734</v>
+        <v>6696691</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2856,24 +2852,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>2st m stjälk</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2889,27 +2870,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135269228</t>
+          <t>https://artportalen.se/Sighting/135267983</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135269382</v>
+        <v>135269228</v>
       </c>
       <c r="B21" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2936,7 +2917,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2953,10 +2934,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459654</v>
+        <v>459755</v>
       </c>
       <c r="R21" t="n">
-        <v>6696700</v>
+        <v>6696734</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3003,7 +2984,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>silvertejpmarkerad men ej inlagt i artportalen tidigare</t>
+          <t>2st m stjälk</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3030,16 +3011,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135269382</t>
+          <t>https://artportalen.se/Sighting/135269228</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135475860</v>
+        <v>135269382</v>
       </c>
       <c r="B22" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3066,7 +3047,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3079,17 +3060,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Butjärnsberget, Dlr</t>
+          <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459335</v>
+        <v>459654</v>
       </c>
       <c r="R22" t="n">
-        <v>6696521</v>
+        <v>6696700</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3113,12 +3094,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>silvertejpmarkerad men ej inlagt i artportalen tidigare</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3134,16 +3130,131 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269382</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135475860</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Butjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>459335</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6696521</v>
+      </c>
+      <c r="S23" t="n">
+        <v>50</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135475860</t>
         </is>
@@ -3172,6 +3283,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>135269155</v>
       </c>
       <c r="B5" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>135269308</v>
       </c>
       <c r="B6" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135661458</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>135267983</v>
       </c>
       <c r="B20" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>135269228</v>
       </c>
       <c r="B21" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>135269382</v>
       </c>
       <c r="B22" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>135475860</v>
       </c>
       <c r="B23" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -998,48 +998,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174966</v>
+        <v>135269155</v>
       </c>
       <c r="B5" t="n">
-        <v>80432</v>
+        <v>79441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459432</v>
+        <v>459667</v>
       </c>
       <c r="R5" t="n">
-        <v>6696511</v>
+        <v>6696747</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,27 +1066,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal stor sälg.</t>
+          <t>i Tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,33 +1095,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127174966</t>
+          <t>https://artportalen.se/Sighting/135269155</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127174601</v>
+        <v>135269308</v>
       </c>
       <c r="B6" t="n">
-        <v>99118</v>
+        <v>79441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,46 +1130,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459523</v>
+        <v>459706</v>
       </c>
       <c r="R6" t="n">
-        <v>6696489</v>
+        <v>6696723</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,27 +1187,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera blommande stänglar</t>
+          <t>Högt upp i Tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,33 +1216,34 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127174601</t>
+          <t>https://artportalen.se/Sighting/135269308</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174720</v>
+        <v>135661458</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>79441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,46 +1251,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459424</v>
+        <v>459376</v>
       </c>
       <c r="R7" t="n">
-        <v>6696607</v>
+        <v>6696540</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,22 +1308,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,77 +1327,69 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127174720</t>
+          <t>https://artportalen.se/Sighting/135661458</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127175097</v>
+        <v>127174966</v>
       </c>
       <c r="B8" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459453</v>
+        <v>459432</v>
       </c>
       <c r="R8" t="n">
-        <v>6696400</v>
+        <v>6696511</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1441,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1431,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gammal stor sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,63 +1462,59 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127175097</t>
+          <t>https://artportalen.se/Sighting/127174966</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127242762</v>
+        <v>135475891</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>57977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459419</v>
+        <v>459499</v>
       </c>
       <c r="R9" t="n">
-        <v>6696311</v>
+        <v>6696373</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1560,12 +1541,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>födosökshack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,7 +1560,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1592,52 +1577,48 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127242762</t>
+          <t>https://artportalen.se/Sighting/135475891</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127243033</v>
+        <v>135269344</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1645,13 +1626,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459437</v>
+        <v>459672</v>
       </c>
       <c r="R10" t="n">
-        <v>6696342</v>
+        <v>6696703</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1675,12 +1656,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,70 +1685,65 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127243033</t>
+          <t>https://artportalen.se/Sighting/135269344</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127243245</v>
+        <v>135269440</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1760,13 +1751,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459450</v>
+        <v>459559</v>
       </c>
       <c r="R11" t="n">
-        <v>6696315</v>
+        <v>6696684</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1790,12 +1781,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,31 +1810,30 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127243245</t>
+          <t>https://artportalen.se/Sighting/135269440</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127243529</v>
+        <v>127174601</v>
       </c>
       <c r="B12" t="n">
         <v>99118</v>
@@ -1858,7 +1863,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1866,22 +1871,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459477</v>
+        <v>459523</v>
       </c>
       <c r="R12" t="n">
-        <v>6696357</v>
+        <v>6696489</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1908,42 +1910,56 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Flera blommande stänglar</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127243529</t>
+          <t>https://artportalen.se/Sighting/127174601</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127244478</v>
+        <v>127174720</v>
       </c>
       <c r="B13" t="n">
         <v>99118</v>
@@ -1976,23 +1992,24 @@
           <t>20</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459418</v>
+        <v>459424</v>
       </c>
       <c r="R13" t="n">
-        <v>6696365</v>
+        <v>6696607</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2019,36 +2036,1227 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/127174720</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127175097</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>459453</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6696400</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>malou lundin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>malou lundin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127175097</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127242762</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>459419</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6696311</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127242762</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127243033</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>459437</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6696342</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127243033</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127243245</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>459450</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6696315</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127243245</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127243529</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>459477</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6696357</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127243529</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127244478</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>459418</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6696365</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/127244478</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135267983</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Butjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>459580</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6696691</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135267983</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135269228</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>459755</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6696734</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2st m stjälk</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269228</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135269382</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>459654</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6696700</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>silvertejpmarkerad men ej inlagt i artportalen tidigare</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269382</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135475860</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Butjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>459335</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6696521</v>
+      </c>
+      <c r="S23" t="n">
+        <v>50</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135475860</t>
         </is>
       </c>
     </row>
@@ -2066,6 +3274,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -2775,7 +2775,7 @@
         <v>135267983</v>
       </c>
       <c r="B20" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>135269228</v>
       </c>
       <c r="B21" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>135269382</v>
       </c>
       <c r="B22" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>135475860</v>
       </c>
       <c r="B23" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>135661458</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>135475891</v>
       </c>
       <c r="B9" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>135475860</v>
       </c>
       <c r="B23" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>135661458</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>135661458</v>
       </c>
       <c r="B7" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>135661458</v>
       </c>
       <c r="B7" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33962-2025 artfynd.xlsx
+++ b/artfynd/A 33962-2025 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>135661458</v>
       </c>
       <c r="B7" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
